--- a/java/verify/fixtures/表头带注释（ods_t_head_note）.xlsx
+++ b/java/verify/fixtures/表头带注释（ods_t_head_note）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,31 @@
           <t>（备注说明）</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>发布日期：yyyy-MM-dd</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>填表日期 yyyymmdd</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>发布日期(YYYYMMDD</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>登记日期〖yyyy/MM/dd〗</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>累年月日降水量≥1.0mm平均日数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +514,31 @@
           <t>x</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2008-05-21</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20080522</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20080523</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2008-05-24</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +574,31 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>y</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2009-01-04</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20090105</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20090106</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2009-01-07</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
